--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/region-de-coquimbo.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/region-de-coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1079505-463-CM26</t>
+          <t>1079505-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>48959.79</v>
+        <v>34477.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057438-233-CM26</t>
+          <t>1057440-130-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7137.61</v>
+        <v>66529.92999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2146-451-CM26</t>
+          <t>3276-5-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14665.43</v>
+        <v>21897.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1660-751-CM26</t>
+          <t>1289649-20-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>26977.21</v>
+        <v>14944.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2147-397-CM26</t>
+          <t>1079505-56-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13667.31</v>
+        <v>30815.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1229788-202-CM26</t>
+          <t>2554-1-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>25827.57</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1395-688-CM26</t>
+          <t>2554-2-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>40696.68</v>
+        <v>752.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2125-1731-CM26</t>
+          <t>3532-9-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>77044.88</v>
+        <v>965.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2145-809-CM26</t>
+          <t>1079505-183-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>29721.7</v>
+        <v>35184.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057440-470-CM26</t>
+          <t>2553-6-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,6 +1118,2080 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>1944.49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2552-4-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>3126.43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2554-10-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>2704.59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2554-12-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>772.74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1079505-279-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>34714.11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2030-21-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>60.902.052-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>281.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>707418-44-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>3784.54</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1079505-420-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>38788.27</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>707418-54-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>9463.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>953-165-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>60.511.040-1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>2131.56</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>931-100-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>795.5700000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>973153-8-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>60.803.435-8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>338.42</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>973153-7-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>60.803.435-8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>345.94</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1079505-538-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>33552.98</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3532-91-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>81.925.500-8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>26466.95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1079505-620-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>37687.59</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2208-19-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.803.000-k</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>517.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>973153-10-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>60.803.435-8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>219.57</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1079505-763-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>35746.86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>697055-60-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>436.21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1079505-913-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>36083.85</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>707418-136-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>3734.65</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>707418-138-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>28741.75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1079505-967-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>3405.15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3532-152-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>81.925.500-8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>172.05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1079505-463-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>48959.79</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1057438-233-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.606.401-0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>7137.61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2146-451-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.606.405-3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>14665.43</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1660-751-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.606.408-8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>26977.21</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2147-397-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.606.406-1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>13667.31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1229788-202-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>25827.57</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1395-688-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>40696.68</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2125-1731-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>77044.88</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2145-809-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.606.409-6</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>29721.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1057440-470-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
         <v>8725.440000000001</v>
       </c>
     </row>
